--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eclipse\Desktop\Automation-Testing-2025\Eclipse\Automation\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3237860-AC04-4564-B149-A95D391A9E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78D438C-6A12-4AB0-AB33-446F0E87DD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -19559,7 +19559,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>850</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19613,7 +19613,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78D438C-6A12-4AB0-AB33-446F0E87DD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAD4518-2E89-4B68-AD80-AE3D8B9B80F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19280,7 +19280,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M2" s="7">
         <v>46202557</v>
@@ -19289,7 +19289,7 @@
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>
@@ -19559,7 +19559,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>850</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19655,7 +19655,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>100051</v>
+        <v>100061</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAD4518-2E89-4B68-AD80-AE3D8B9B80F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD66C5C-B361-4C7D-BF11-2E60BB30D654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,17 +21,28 @@
     <sheet name="Physical_Deposit_Maker" sheetId="2" r:id="rId6"/>
     <sheet name="Deposite_Assayer_Maker" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="117">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -380,6 +391,9 @@
   <si>
     <t>Complete</t>
   </si>
+  <si>
+    <t>Auto Rejected By CCRL</t>
+  </si>
 </sst>
 </file>
 
@@ -449,7 +463,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +497,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,8 +578,8 @@
     <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1124,7 +1144,7 @@
       <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="26">
         <v>100673000000011</v>
       </c>
       <c r="E7" s="1">
@@ -1208,7 +1228,7 @@
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <v>100673000000011</v>
       </c>
       <c r="E9" s="1">
@@ -1250,7 +1270,7 @@
       <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <v>100673000000011</v>
       </c>
       <c r="E10" s="1">
@@ -1292,7 +1312,7 @@
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <v>100673000000011</v>
       </c>
       <c r="E11" s="1">
@@ -1334,7 +1354,7 @@
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="26">
         <v>100673000000011</v>
       </c>
       <c r="E12" s="1">
@@ -1376,7 +1396,7 @@
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="26">
         <v>100673000000011</v>
       </c>
       <c r="E13" s="1">
@@ -1418,7 +1438,7 @@
       <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="26">
         <v>100673000000011</v>
       </c>
       <c r="E14" s="1">
@@ -1511,7 +1531,9 @@
       <c r="M1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="4"/>
+      <c r="N1" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="O1" s="4"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
@@ -1559,6 +1581,9 @@
       <c r="M2" s="15">
         <v>11</v>
       </c>
+      <c r="N2" s="27" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1570,11 +1595,11 @@
       <c r="C3" s="2">
         <v>100673000000011</v>
       </c>
-      <c r="D3" s="26">
-        <v>9999996</v>
-      </c>
-      <c r="E3" s="26">
-        <v>1000421</v>
+      <c r="D3" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E3" s="1">
+        <v>8211642</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>29</v>
@@ -1583,7 +1608,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="1">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="I3" s="1">
         <v>1.7</v>
@@ -1600,6 +1625,7 @@
       <c r="M3" s="1">
         <v>11</v>
       </c>
+      <c r="N3" s="21"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1641,6 +1667,7 @@
       <c r="M4" s="1">
         <v>11</v>
       </c>
+      <c r="N4" s="21"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1682,6 +1709,7 @@
       <c r="M5" s="1">
         <v>11</v>
       </c>
+      <c r="N5" s="21"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1723,6 +1751,7 @@
       <c r="M6" s="1">
         <v>11</v>
       </c>
+      <c r="N6" s="21"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1764,6 +1793,7 @@
       <c r="M7" s="1">
         <v>11</v>
       </c>
+      <c r="N7" s="21"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1805,6 +1835,7 @@
       <c r="M8" s="1">
         <v>11</v>
       </c>
+      <c r="N8" s="21"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1846,6 +1877,7 @@
       <c r="M9" s="1">
         <v>11</v>
       </c>
+      <c r="N9" s="21"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1887,6 +1919,7 @@
       <c r="M10" s="1">
         <v>11</v>
       </c>
+      <c r="N10" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19559,7 +19592,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>850</v>
+        <v>1275</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19607,13 +19640,13 @@
         <v>179</v>
       </c>
       <c r="AA2" s="1">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="AB2" s="7">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AC2" s="7">
-        <v>7</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD66C5C-B361-4C7D-BF11-2E60BB30D654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0A2A65-A991-4842-BA4E-3D487C581CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -545,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -580,6 +580,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1567,7 +1569,7 @@
         <v>700</v>
       </c>
       <c r="I2" s="15">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J2" s="15" t="s">
         <v>30</v>
@@ -1610,8 +1612,8 @@
       <c r="H3" s="1">
         <v>750</v>
       </c>
-      <c r="I3" s="1">
-        <v>1.7</v>
+      <c r="I3" s="28">
+        <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>30</v>
@@ -1652,8 +1654,8 @@
       <c r="H4" s="1">
         <v>700</v>
       </c>
-      <c r="I4" s="1">
-        <v>1.7</v>
+      <c r="I4" s="28">
+        <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>30</v>
@@ -1680,10 +1682,10 @@
         <v>100673000000011</v>
       </c>
       <c r="D5" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="E5" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>29</v>
@@ -1692,10 +1694,10 @@
         <v>15</v>
       </c>
       <c r="H5" s="1">
-        <v>700</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.7</v>
+        <v>850</v>
+      </c>
+      <c r="I5" s="28">
+        <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>30</v>
@@ -1722,10 +1724,10 @@
         <v>100673000000011</v>
       </c>
       <c r="D6" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="E6" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>29</v>
@@ -1736,8 +1738,8 @@
       <c r="H6" s="1">
         <v>700</v>
       </c>
-      <c r="I6" s="1">
-        <v>1.7</v>
+      <c r="I6" s="28">
+        <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>30</v>
@@ -1778,8 +1780,8 @@
       <c r="H7" s="1">
         <v>700</v>
       </c>
-      <c r="I7" s="1">
-        <v>1.7</v>
+      <c r="I7" s="28">
+        <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>30</v>
@@ -1806,10 +1808,10 @@
         <v>100673000000011</v>
       </c>
       <c r="D8" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="E8" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>29</v>
@@ -1820,8 +1822,8 @@
       <c r="H8" s="1">
         <v>700</v>
       </c>
-      <c r="I8" s="1">
-        <v>1.7</v>
+      <c r="I8" s="28">
+        <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>30</v>
@@ -1862,8 +1864,8 @@
       <c r="H9" s="1">
         <v>700</v>
       </c>
-      <c r="I9" s="1">
-        <v>1.7</v>
+      <c r="I9" s="28">
+        <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>30</v>
@@ -1904,8 +1906,8 @@
       <c r="H10" s="1">
         <v>700</v>
       </c>
-      <c r="I10" s="1">
-        <v>1.7</v>
+      <c r="I10" s="28">
+        <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>30</v>
@@ -18468,11 +18470,11 @@
       <c r="D5" s="7">
         <v>11</v>
       </c>
-      <c r="E5" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1000421</v>
+      <c r="E5" s="29">
+        <v>9996059</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5750013</v>
       </c>
       <c r="G5" s="11">
         <v>100673000000011</v>
@@ -19592,7 +19594,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>1275</v>
+        <v>850</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19640,13 +19642,13 @@
         <v>179</v>
       </c>
       <c r="AA2" s="1">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="AB2" s="7">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="AC2" s="7">
-        <v>750</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0A2A65-A991-4842-BA4E-3D487C581CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590DD063-0289-48CA-A760-305492475E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="116">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -318,9 +318,6 @@
   </si>
   <si>
     <t>NetWeightPerPackList</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RP_Deposite_Request_Agriculture_Maker.bags</t>
   </si>
   <si>
     <t>Quality_Stand</t>
@@ -913,7 +910,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -948,7 +945,7 @@
         <v>1.7</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L2" s="15" t="s">
         <v>15</v>
@@ -957,7 +954,7 @@
         <v>15</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -992,7 +989,7 @@
         <v>1.7</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L3" s="15" t="s">
         <v>15</v>
@@ -1001,7 +998,7 @@
         <v>15</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1036,7 +1033,7 @@
         <v>1.7</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L4" s="15" t="s">
         <v>15</v>
@@ -1045,7 +1042,7 @@
         <v>15</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1080,7 +1077,7 @@
         <v>1.7</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L5" s="15" t="s">
         <v>15</v>
@@ -1089,7 +1086,7 @@
         <v>15</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1124,7 +1121,7 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L6" s="15" t="s">
         <v>15</v>
@@ -1133,7 +1130,7 @@
         <v>15</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1168,7 +1165,7 @@
         <v>1.7</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>15</v>
@@ -1210,7 +1207,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>15</v>
@@ -1252,7 +1249,7 @@
         <v>1.7</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>15</v>
@@ -1294,7 +1291,7 @@
         <v>1.7</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>15</v>
@@ -1336,7 +1333,7 @@
         <v>1.7</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>15</v>
@@ -1378,7 +1375,7 @@
         <v>1.7</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>15</v>
@@ -1420,7 +1417,7 @@
         <v>1.7</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>15</v>
@@ -1462,7 +1459,7 @@
         <v>1.7</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>15</v>
@@ -1534,7 +1531,7 @@
         <v>28</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O1" s="4"/>
       <c r="P1" s="3"/>
@@ -1584,7 +1581,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -1778,10 +1775,10 @@
         <v>15</v>
       </c>
       <c r="H7" s="1">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I7" s="28">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>30</v>
@@ -1945,25 +1942,25 @@
         <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E1" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="G1" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>20</v>
@@ -1990,7 +1987,7 @@
         <v>27</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
@@ -1998,22 +1995,22 @@
         <v>5555509</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" s="22">
         <v>2025</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="23">
         <v>100673001212128</v>
@@ -2034,7 +2031,7 @@
         <v>0.5</v>
       </c>
       <c r="N2" s="22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O2" s="22" t="s">
         <v>15</v>
@@ -2043,7 +2040,7 @@
         <v>15</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
@@ -2051,22 +2048,22 @@
         <v>5555534</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" s="22">
         <v>2025</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H3" s="23">
         <v>100673001212128</v>
@@ -2087,7 +2084,7 @@
         <v>0.5</v>
       </c>
       <c r="N3" s="22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O3" s="22" t="s">
         <v>15</v>
@@ -2096,7 +2093,7 @@
         <v>15</v>
       </c>
       <c r="Q3" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
@@ -2104,22 +2101,22 @@
         <v>5555535</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E4" s="7">
         <v>2025</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H4" s="11">
         <v>100673001212128</v>
@@ -2140,7 +2137,7 @@
         <v>0.5</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>15</v>
@@ -2155,22 +2152,22 @@
         <v>5555536</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" s="7">
         <v>2025</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H5" s="11">
         <v>100673001212128</v>
@@ -2191,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>15</v>
@@ -2206,22 +2203,22 @@
         <v>5555537</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E6" s="7">
         <v>2025</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H6" s="11">
         <v>100673001212128</v>
@@ -2242,7 +2239,7 @@
         <v>0.5</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O6" s="7" t="s">
         <v>15</v>
@@ -2257,22 +2254,22 @@
         <v>5555538</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" s="7">
         <v>2025</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H7" s="11">
         <v>100673001212128</v>
@@ -2293,7 +2290,7 @@
         <v>0.5</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>15</v>
@@ -2308,22 +2305,22 @@
         <v>5555539</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E8" s="7">
         <v>2025</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H8" s="11">
         <v>100673001212128</v>
@@ -2344,7 +2341,7 @@
         <v>0.5</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>15</v>
@@ -2359,22 +2356,22 @@
         <v>5555540</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9" s="7">
         <v>2025</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H9" s="11">
         <v>100673001212128</v>
@@ -2395,7 +2392,7 @@
         <v>0.5</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>15</v>
@@ -2410,22 +2407,22 @@
         <v>5555541</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" s="7">
         <v>2025</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H10" s="11">
         <v>100673001212128</v>
@@ -2446,7 +2443,7 @@
         <v>0.5</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O10" s="7" t="s">
         <v>15</v>
@@ -2461,22 +2458,22 @@
         <v>5555542</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11" s="7">
         <v>2025</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H11" s="11">
         <v>100673001212128</v>
@@ -2497,7 +2494,7 @@
         <v>0.5</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>15</v>
@@ -2512,22 +2509,22 @@
         <v>5555543</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" s="7">
         <v>2025</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H12" s="11">
         <v>100673001212128</v>
@@ -2548,7 +2545,7 @@
         <v>0.5</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O12" s="7" t="s">
         <v>15</v>
@@ -2563,22 +2560,22 @@
         <v>5555544</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E13" s="7">
         <v>2025</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H13" s="11">
         <v>100673001212128</v>
@@ -2599,7 +2596,7 @@
         <v>0.5</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>15</v>
@@ -2614,22 +2611,22 @@
         <v>5555545</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E14" s="7">
         <v>2025</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H14" s="11">
         <v>100673001212128</v>
@@ -2650,7 +2647,7 @@
         <v>0.5</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O14" s="7" t="s">
         <v>15</v>
@@ -2665,22 +2662,22 @@
         <v>5555546</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E15" s="7">
         <v>2025</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H15" s="11">
         <v>100673001212128</v>
@@ -2701,7 +2698,7 @@
         <v>0.5</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>15</v>
@@ -5785,22 +5782,22 @@
         <v>5555547</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E16" s="7">
         <v>2025</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H16" s="11">
         <v>100673001212128</v>
@@ -5821,7 +5818,7 @@
         <v>0.5</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>15</v>
@@ -8905,22 +8902,22 @@
         <v>5555548</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E17" s="7">
         <v>2025</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H17" s="11">
         <v>100673001212128</v>
@@ -8941,7 +8938,7 @@
         <v>0.5</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>15</v>
@@ -12025,22 +12022,22 @@
         <v>5555549</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" s="7">
         <v>2025</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H18" s="11">
         <v>100673001212128</v>
@@ -12061,7 +12058,7 @@
         <v>0.5</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>15</v>
@@ -15145,22 +15142,22 @@
         <v>5555550</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E19" s="7">
         <v>2025</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H19" s="11">
         <v>100673001212128</v>
@@ -15181,7 +15178,7 @@
         <v>0.5</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>15</v>
@@ -19362,8 +19359,8 @@
       <c r="AA2" s="7">
         <v>179</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>92</v>
+      <c r="AB2" s="7">
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -19563,7 +19560,7 @@
         <v>58</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
@@ -19588,7 +19585,7 @@
         <v>46202555</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J2" s="1">
         <v>130000</v>
@@ -19645,7 +19642,7 @@
         <v>900</v>
       </c>
       <c r="AB2" s="7">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="7">
         <v>5</v>
@@ -19670,33 +19667,33 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>56</v>
       </c>
       <c r="C1" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>110</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>100061</v>
+        <v>100063</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D2" s="21">
         <v>1345645</v>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590DD063-0289-48CA-A760-305492475E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89357190-F04F-459E-B4BE-DA1A403B6F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -19687,7 +19687,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>100063</v>
+        <v>100064</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89357190-F04F-459E-B4BE-DA1A403B6F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D906D3-B22B-4508-B994-FD9437667009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="119">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -391,6 +391,15 @@
   <si>
     <t>Auto Rejected By CCRL</t>
   </si>
+  <si>
+    <t>Phy</t>
+  </si>
+  <si>
+    <t>sample_ID</t>
+  </si>
+  <si>
+    <t>Used</t>
+  </si>
 </sst>
 </file>
 
@@ -460,7 +469,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,6 +512,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -542,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -578,7 +593,11 @@
     <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1134,130 +1153,136 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="30">
         <v>5555526</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="31">
         <v>100673000000011</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="30">
         <v>9999996</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="30">
         <v>1000421</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="30">
         <v>1</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="30">
         <v>500</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="30">
         <v>1.7</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="21"/>
+      <c r="N7" s="33" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="30">
         <v>5555527</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="31">
         <v>100673000000011</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="30">
         <v>9999996</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="30">
         <v>1000421</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="30">
         <v>1</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="30">
         <v>700</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="30">
         <v>1.7</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="21"/>
+      <c r="N8" s="33" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="30">
         <v>5555528</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="31">
         <v>100673000000011</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="30">
         <v>9999996</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="30">
         <v>1000421</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="30">
         <v>1</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="30">
         <v>500</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="30">
         <v>1.7</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="21"/>
+      <c r="N9" s="33" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1930,6 +1955,7 @@
   <dimension ref="A1:XEX19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.140625" customWidth="1"/>
@@ -2097,8 +2123,8 @@
       </c>
     </row>
     <row r="4" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>5555535</v>
+      <c r="A4" s="11">
+        <v>152222092025</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>93</v>
@@ -2119,13 +2145,13 @@
         <v>100</v>
       </c>
       <c r="H4" s="11">
-        <v>100673001212128</v>
+        <v>120733340001479</v>
       </c>
       <c r="I4" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J4" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K4" s="7">
         <v>100</v>
@@ -2170,13 +2196,13 @@
         <v>100</v>
       </c>
       <c r="H5" s="11">
-        <v>100673001212128</v>
+        <v>120733340001479</v>
       </c>
       <c r="I5" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J5" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K5" s="7">
         <v>100</v>
@@ -2221,13 +2247,13 @@
         <v>100</v>
       </c>
       <c r="H6" s="11">
-        <v>100673001212128</v>
+        <v>120733340001479</v>
       </c>
       <c r="I6" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J6" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K6" s="7">
         <v>100</v>
@@ -2272,13 +2298,13 @@
         <v>100</v>
       </c>
       <c r="H7" s="11">
-        <v>100673001212128</v>
+        <v>120733340001479</v>
       </c>
       <c r="I7" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J7" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K7" s="7">
         <v>100</v>
@@ -2323,13 +2349,13 @@
         <v>100</v>
       </c>
       <c r="H8" s="11">
-        <v>100673001212128</v>
+        <v>120733340001479</v>
       </c>
       <c r="I8" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J8" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K8" s="7">
         <v>100</v>
@@ -2374,13 +2400,13 @@
         <v>100</v>
       </c>
       <c r="H9" s="11">
-        <v>100673001212128</v>
+        <v>120733340001479</v>
       </c>
       <c r="I9" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J9" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K9" s="7">
         <v>100</v>
@@ -2425,13 +2451,13 @@
         <v>100</v>
       </c>
       <c r="H10" s="11">
-        <v>100673001212128</v>
+        <v>120733340001479</v>
       </c>
       <c r="I10" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J10" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K10" s="7">
         <v>100</v>
@@ -15163,7 +15189,7 @@
         <v>100673001212128</v>
       </c>
       <c r="I19" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J19" s="1">
         <v>8211642</v>
@@ -18458,46 +18484,48 @@
       <c r="A5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="22">
         <v>5555554</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="22">
         <v>11</v>
       </c>
       <c r="E5" s="29">
         <v>9996059</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="24">
         <v>5750013</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="23">
         <v>100673000000011</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="22">
         <v>1003</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="22">
         <v>10</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="22">
         <v>10</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="22">
         <v>50</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="O5" s="7"/>
+      <c r="O5" s="22" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -19314,8 +19342,8 @@
       <c r="L2" s="7">
         <v>10</v>
       </c>
-      <c r="M2" s="7">
-        <v>46202557</v>
+      <c r="M2" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
@@ -19591,7 +19619,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>850</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19645,7 +19673,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D906D3-B22B-4508-B994-FD9437667009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05EC207-3F64-4505-B2EE-2DFC50A94285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="4" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>152222092025</v>
+        <v>5555535</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>93</v>
@@ -19592,8 +19592,12 @@
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+      <c r="A2" s="1">
+        <v>22442</v>
+      </c>
+      <c r="B2" s="1">
+        <v>232324</v>
+      </c>
       <c r="C2" s="1">
         <v>500</v>
       </c>
